--- a/data/trans_orig/P16A12-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>32641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57264</t>
+          <t>56684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23419</t>
+          <t>23602</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46216</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61915</t>
+          <t>62189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95009</t>
+          <t>94306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>635730</t>
+          <t>636310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>661400</t>
+          <t>660353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>642135</t>
+          <t>643055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664932</t>
+          <t>664749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1286336</t>
+          <t>1287039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1319430</t>
+          <t>1319156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>46418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77316</t>
+          <t>75511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57925</t>
+          <t>57868</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91004</t>
+          <t>93203</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111808</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155250</t>
+          <t>155463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>884484</t>
+          <t>886289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>915577</t>
+          <t>915382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>877389</t>
+          <t>875190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910468</t>
+          <t>910525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1774943</t>
+          <t>1774730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1818385</t>
+          <t>1819762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>22016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43634</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30383</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55072</t>
+          <t>54380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57713</t>
+          <t>57545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>91371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634875</t>
+          <t>634600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656722</t>
+          <t>656493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>628769</t>
+          <t>629461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653458</t>
+          <t>654484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1272022</t>
+          <t>1270979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1304637</t>
+          <t>1304805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>39284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62388</t>
+          <t>63680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42998</t>
+          <t>44329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73791</t>
+          <t>74043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88150</t>
+          <t>89909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127583</t>
+          <t>127947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>879834</t>
+          <t>878542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>904387</t>
+          <t>902938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>964821</t>
+          <t>964569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995614</t>
+          <t>994283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1853251</t>
+          <t>1852887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1892684</t>
+          <t>1890925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>159289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209442</t>
+          <t>209717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177613</t>
+          <t>178922</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>237097</t>
+          <t>234057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>349023</t>
+          <t>352733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424353</t>
+          <t>426803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3066083</t>
+          <t>3065808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3116555</t>
+          <t>3116236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3142100</t>
+          <t>3145140</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3201584</t>
+          <t>3200275</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6230369</t>
+          <t>6227919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6305699</t>
+          <t>6301989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36748</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64033</t>
+          <t>63516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37154</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64161</t>
+          <t>64543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80542</t>
+          <t>80294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120082</t>
+          <t>119632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>636731</t>
+          <t>637248</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>664016</t>
+          <t>665870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>630127</t>
+          <t>629745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657134</t>
+          <t>657332</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1274969</t>
+          <t>1275419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1314509</t>
+          <t>1314757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52005</t>
+          <t>51629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84327</t>
+          <t>83407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66173</t>
+          <t>65839</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100453</t>
+          <t>101744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122609</t>
+          <t>124729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>173808</t>
+          <t>172176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>933620</t>
+          <t>934540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>965942</t>
+          <t>966318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>927322</t>
+          <t>926031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>961602</t>
+          <t>961936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1871915</t>
+          <t>1873547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1923114</t>
+          <t>1920994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35996</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>64624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82923</t>
+          <t>83088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93564</t>
+          <t>95709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137818</t>
+          <t>140461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692685</t>
+          <t>691914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>720542</t>
+          <t>720878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693360</t>
+          <t>693195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>724388</t>
+          <t>725435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1395003</t>
+          <t>1392360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1439257</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70411</t>
+          <t>67428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109036</t>
+          <t>107208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83770</t>
+          <t>85774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124481</t>
+          <t>123936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165170</t>
+          <t>165558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215884</t>
+          <t>221671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836894</t>
+          <t>838722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875519</t>
+          <t>878502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>924282</t>
+          <t>924827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964993</t>
+          <t>962989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1778810</t>
+          <t>1773023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1829524</t>
+          <t>1829136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>219446</t>
+          <t>221138</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>282832</t>
+          <t>284347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>269319</t>
+          <t>266721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335355</t>
+          <t>333511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>502682</t>
+          <t>502880</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>599412</t>
+          <t>592595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3138347</t>
+          <t>3136832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3201733</t>
+          <t>3200041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3211755</t>
+          <t>3213599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3277791</t>
+          <t>3280389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6368877</t>
+          <t>6375694</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6465607</t>
+          <t>6465409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52125</t>
+          <t>51692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84010</t>
+          <t>81115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>44871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74429</t>
+          <t>77300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103688</t>
+          <t>105076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146201</t>
+          <t>148200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>590790</t>
+          <t>593685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>622675</t>
+          <t>623108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>598410</t>
+          <t>595539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>628943</t>
+          <t>627968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1201438</t>
+          <t>1199439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1243951</t>
+          <t>1242563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64812</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>98527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61825</t>
+          <t>62512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98899</t>
+          <t>98597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136860</t>
+          <t>136279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>190196</t>
+          <t>183782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924907</t>
+          <t>923904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>957619</t>
+          <t>957089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>944014</t>
+          <t>944316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>981088</t>
+          <t>980401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1875148</t>
+          <t>1881562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1928484</t>
+          <t>1929065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>53876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87874</t>
+          <t>86950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46057</t>
+          <t>44877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77329</t>
+          <t>77743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110416</t>
+          <t>108476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156365</t>
+          <t>156027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671678</t>
+          <t>672602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>704931</t>
+          <t>705676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>707682</t>
+          <t>707268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>738954</t>
+          <t>740134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1388198</t>
+          <t>1388536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1434147</t>
+          <t>1436087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53742</t>
+          <t>53902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83274</t>
+          <t>83852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98318</t>
+          <t>98992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126818</t>
+          <t>125912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175308</t>
+          <t>172943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854293</t>
+          <t>853715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883825</t>
+          <t>883665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945461</t>
+          <t>944787</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>982301</t>
+          <t>980300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1806038</t>
+          <t>1808403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1854528</t>
+          <t>1855434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253157</t>
+          <t>252972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>316850</t>
+          <t>316276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,82 +6014,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>277943</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>247421</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>316075</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>561750</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>517427</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>610129</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>277943</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>246106</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>313433</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>561750</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>517317</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>608821</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3077500</t>
+          <t>3078074</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3141193</t>
+          <t>3141378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3231109</t>
+          <t>3228467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3298436</t>
+          <t>3297121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6330071</t>
+          <t>6328763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6421575</t>
+          <t>6421465</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49114</t>
+          <t>49557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73634</t>
+          <t>73760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52288</t>
+          <t>52426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>73950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108360</t>
+          <t>108521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140672</t>
+          <t>140186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>561807</t>
+          <t>561681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>586327</t>
+          <t>585884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>602235</t>
+          <t>601802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>623464</t>
+          <t>623326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1170522</t>
+          <t>1171008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1202834</t>
+          <t>1202673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>38550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105094</t>
+          <t>103309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61250</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85157</t>
+          <t>85825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98260</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177888</t>
+          <t>178031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1087770</t>
+          <t>1089555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1151668</t>
+          <t>1154314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>872949</t>
+          <t>872281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>896856</t>
+          <t>896213</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1973083</t>
+          <t>1972940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2052711</t>
+          <t>2051284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42929</t>
+          <t>42749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70129</t>
+          <t>68965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59748</t>
+          <t>60088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66376</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121829</t>
+          <t>122063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633555</t>
+          <t>634719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660755</t>
+          <t>660935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>873052</t>
+          <t>872712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>910946</t>
+          <t>913001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1514655</t>
+          <t>1514421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1570108</t>
+          <t>1571915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72376</t>
+          <t>72444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103673</t>
+          <t>105480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58935</t>
+          <t>59165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90148</t>
+          <t>88478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140616</t>
+          <t>137925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184215</t>
+          <t>183167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>823158</t>
+          <t>821351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>854455</t>
+          <t>854387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1001226</t>
+          <t>1002896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1032439</t>
+          <t>1032209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1833990</t>
+          <t>1835038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1877589</t>
+          <t>1880280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>222751</t>
+          <t>211549</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>319679</t>
+          <t>319523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203062</t>
+          <t>207611</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>280081</t>
+          <t>281874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470477</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>588927</t>
+          <t>586496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3139141</t>
+          <t>3139297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3236069</t>
+          <t>3247271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3377952</t>
+          <t>3376159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3454971</t>
+          <t>3450422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6527926</t>
+          <t>6530357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6646376</t>
+          <t>6655622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A12-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32641</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56684</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23602</t>
+          <t>23104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>46276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62189</t>
+          <t>61522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94306</t>
+          <t>96185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>636310</t>
+          <t>635448</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>660353</t>
+          <t>660927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>643055</t>
+          <t>642075</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664749</t>
+          <t>665247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1287039</t>
+          <t>1285160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1319156</t>
+          <t>1319823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46418</t>
+          <t>46815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75511</t>
+          <t>78563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57868</t>
+          <t>57429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93203</t>
+          <t>90670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>111480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155463</t>
+          <t>156425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>886289</t>
+          <t>883237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>915382</t>
+          <t>914985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>875190</t>
+          <t>877723</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910525</t>
+          <t>910964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1774730</t>
+          <t>1773768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1819762</t>
+          <t>1818713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43909</t>
+          <t>43630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54380</t>
+          <t>54185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57545</t>
+          <t>57426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91371</t>
+          <t>90416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634600</t>
+          <t>634879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656493</t>
+          <t>656757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>629461</t>
+          <t>629656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654484</t>
+          <t>653601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1270979</t>
+          <t>1271934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1304805</t>
+          <t>1304924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39284</t>
+          <t>36878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63680</t>
+          <t>62920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>43534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74043</t>
+          <t>72097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89909</t>
+          <t>89587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127947</t>
+          <t>128139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>878542</t>
+          <t>879302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902938</t>
+          <t>905344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>964569</t>
+          <t>966515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>994283</t>
+          <t>995078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1852887</t>
+          <t>1852695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1890925</t>
+          <t>1891247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159289</t>
+          <t>158228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209717</t>
+          <t>209691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>178922</t>
+          <t>177006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>234057</t>
+          <t>231537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>352733</t>
+          <t>352579</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>426803</t>
+          <t>428694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3065808</t>
+          <t>3065834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3116236</t>
+          <t>3117297</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3145140</t>
+          <t>3147660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3200275</t>
+          <t>3202191</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6227919</t>
+          <t>6226028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6301989</t>
+          <t>6302143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63516</t>
+          <t>64207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36956</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64543</t>
+          <t>64449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80294</t>
+          <t>78873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119632</t>
+          <t>117654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>637248</t>
+          <t>636557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665870</t>
+          <t>664502</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629745</t>
+          <t>629839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657332</t>
+          <t>657614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1275419</t>
+          <t>1277397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1314757</t>
+          <t>1316178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51629</t>
+          <t>52806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83407</t>
+          <t>83796</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65839</t>
+          <t>67385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101744</t>
+          <t>102283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124729</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172176</t>
+          <t>172188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>934540</t>
+          <t>934151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>966318</t>
+          <t>965141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926031</t>
+          <t>925492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>961936</t>
+          <t>960390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1873547</t>
+          <t>1873535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1920994</t>
+          <t>1921769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>36327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83088</t>
+          <t>82420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95709</t>
+          <t>96223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140461</t>
+          <t>138401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>691914</t>
+          <t>691813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>720878</t>
+          <t>720211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693195</t>
+          <t>693863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>725435</t>
+          <t>725868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1392360</t>
+          <t>1394420</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1437112</t>
+          <t>1436598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67428</t>
+          <t>70874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107208</t>
+          <t>108311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123936</t>
+          <t>122817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165558</t>
+          <t>166344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>221671</t>
+          <t>219231</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>838722</t>
+          <t>837619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878502</t>
+          <t>875056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>924827</t>
+          <t>925946</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>962989</t>
+          <t>963513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1773023</t>
+          <t>1775463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1829136</t>
+          <t>1828350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>221138</t>
+          <t>218039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>284347</t>
+          <t>282352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266721</t>
+          <t>267237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>333511</t>
+          <t>332385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>502880</t>
+          <t>506456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>592595</t>
+          <t>597037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3136832</t>
+          <t>3138827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3200041</t>
+          <t>3203140</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3213599</t>
+          <t>3214725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3280389</t>
+          <t>3279873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6375694</t>
+          <t>6371252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6465409</t>
+          <t>6461833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51692</t>
+          <t>50152</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81115</t>
+          <t>81335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44871</t>
+          <t>44387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77300</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105076</t>
+          <t>103143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148200</t>
+          <t>145407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>593685</t>
+          <t>593465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>623108</t>
+          <t>624648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>595539</t>
+          <t>597865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>627968</t>
+          <t>628452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1199439</t>
+          <t>1202232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1242563</t>
+          <t>1244496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>64991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98527</t>
+          <t>99768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62512</t>
+          <t>61701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98597</t>
+          <t>98342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136279</t>
+          <t>135316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183782</t>
+          <t>185558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>923904</t>
+          <t>922663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>957089</t>
+          <t>957440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>944316</t>
+          <t>944571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>980401</t>
+          <t>981212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1881562</t>
+          <t>1879786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1929065</t>
+          <t>1930028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86950</t>
+          <t>89431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44877</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77743</t>
+          <t>76611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108476</t>
+          <t>112498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156027</t>
+          <t>159799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672602</t>
+          <t>670121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>705676</t>
+          <t>704205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>707268</t>
+          <t>708400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>740134</t>
+          <t>739090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1388536</t>
+          <t>1384764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1436087</t>
+          <t>1432065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53902</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83852</t>
+          <t>84054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98992</t>
+          <t>97690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125912</t>
+          <t>123844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172943</t>
+          <t>171510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853715</t>
+          <t>853513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883665</t>
+          <t>883246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>944787</t>
+          <t>946089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>980300</t>
+          <t>980381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1808403</t>
+          <t>1809836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1855434</t>
+          <t>1857502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>252972</t>
+          <t>252521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>316276</t>
+          <t>313703</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>247421</t>
+          <t>245451</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>316075</t>
+          <t>315598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>517427</t>
+          <t>517451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>610129</t>
+          <t>605904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3078074</t>
+          <t>3080647</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3141378</t>
+          <t>3141829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3228467</t>
+          <t>3228944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3297121</t>
+          <t>3299091</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6328763</t>
+          <t>6332988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6421465</t>
+          <t>6421441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>61105</t>
+          <t>65891</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49557</t>
+          <t>51702</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73760</t>
+          <t>80773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62733</t>
+          <t>66671</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52426</t>
+          <t>56477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73950</t>
+          <t>77491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>123839</t>
+          <t>132562</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108521</t>
+          <t>117463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140186</t>
+          <t>152494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>574336</t>
+          <t>624819</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>561681</t>
+          <t>609937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>585884</t>
+          <t>639008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>613019</t>
+          <t>666442</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>601802</t>
+          <t>655622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>623326</t>
+          <t>676636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1187355</t>
+          <t>1291261</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1171008</t>
+          <t>1271329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1202673</t>
+          <t>1306360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77779</t>
+          <t>86499</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>71114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103309</t>
+          <t>104029</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73395</t>
+          <t>80802</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61893</t>
+          <t>69264</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85825</t>
+          <t>94669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>151174</t>
+          <t>167301</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99687</t>
+          <t>148482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178031</t>
+          <t>190059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1115085</t>
+          <t>962418</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1089555</t>
+          <t>944888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1154314</t>
+          <t>977803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>884711</t>
+          <t>990036</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>872281</t>
+          <t>976169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>896213</t>
+          <t>1001574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1999797</t>
+          <t>1952454</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1972940</t>
+          <t>1929696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2051284</t>
+          <t>1971273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55605</t>
+          <t>62678</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42749</t>
+          <t>50024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68965</t>
+          <t>79666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42932</t>
+          <t>47588</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60088</t>
+          <t>58408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>98536</t>
+          <t>110266</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>94916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122063</t>
+          <t>129901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>648079</t>
+          <t>739408</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634719</t>
+          <t>722420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660935</t>
+          <t>752062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>889868</t>
+          <t>764075</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>872712</t>
+          <t>753255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>913001</t>
+          <t>774137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1537948</t>
+          <t>1503482</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1514421</t>
+          <t>1483847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1571915</t>
+          <t>1518832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87620</t>
+          <t>91089</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>76079</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105480</t>
+          <t>107828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74657</t>
+          <t>82185</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59165</t>
+          <t>68289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88478</t>
+          <t>96203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>162277</t>
+          <t>173274</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>152230</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183167</t>
+          <t>195991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>839211</t>
+          <t>898973</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>821351</t>
+          <t>882234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>854387</t>
+          <t>913983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1016717</t>
+          <t>1034846</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002896</t>
+          <t>1020828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1032209</t>
+          <t>1048742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1855928</t>
+          <t>1933819</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1835038</t>
+          <t>1911102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1880280</t>
+          <t>1954863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,69 +7941,69 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>282108</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>211549</t>
+          <t>277521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>319523</t>
+          <t>339357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>277246</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>254897</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>304505</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>253717</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>207611</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>281874</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>927</t>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>535825</t>
+          <t>583403</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>461231</t>
+          <t>545388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>586496</t>
+          <t>624473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -8054,67 +8054,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3176712</t>
+          <t>3225618</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3139297</t>
+          <t>3192418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3247271</t>
+          <t>3254254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4838</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3455399</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3428140</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3477748</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>91,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3404316</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3376159</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3450422</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6581028</t>
+          <t>6681016</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6530357</t>
+          <t>6639946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6655622</t>
+          <t>6719031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
